--- a/content/tz-postuplenie-v-vuz-kitaya.xlsx
+++ b/content/tz-postuplenie-v-vuz-kitaya.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -679,46 +679,58 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Целевой объём блока T123</t>
+          <t>Объём блока T123</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>40 000–45 000 (лимит ≈ 50 000). Вилка поднята второй раз подряд и взята по факту трёх последних статей: 44 901, 44 346, 44 128</t>
+          <t>ПЛАН 40 000–45 000. ФАКТ 45 144 — на 144 знака выше границы, лимит 50 000 не нарушен. Лучшее попадание за четыре статьи</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция инфографики</t>
+          <t>Позиция инфографики</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>26–31 %</t>
+          <t>ПЛАН 26–31 %. ФАКТ 27,3 % (при первой сборке было 25,8 %)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция «Из личного опыта»</t>
+          <t>Позиция «Из личного опыта»</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>36–40 %</t>
+          <t>ПЛАН 36–40 %. ФАКТ 39,2 % (при первой сборке 44,6 %, при второй 41,2 %)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Позиция FAQ</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>74,5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>Ключи и где отрабатываются</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>поступление в вуз китая — тайтл, H1, первый абзац, раздел 1, FAQ. поступление в университет китая — разделы 1 и 3, FAQ. поступление в институт китая — раздел 5, про то, что искать на сайте. поступление в китай из россии — раздел 4, про город и расходы, FAQ. поступление в китай на обучение — раздел 6, короткий список. поступление в китай — ЗАНЯТЫЙ КЛЮЧ, в тайтл НЕ ставим</t>
         </is>
@@ -740,7 +752,7 @@
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -778,7 +790,11 @@
           <t>40 000–45 000, лимит ≈ 50 000</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>45 144 — на 144 знака выше границы. Лучшее попадание за четыре статьи</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -791,7 +807,11 @@
           <t>26–31 %</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>27,3 %. При первой сборке 25,8 % — добавлен абзац перед картинкой</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -804,7 +824,11 @@
           <t>36–40 %</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>39,2 %. Двигала дважды: 44,6 %, потом 41,2 %, потом перенесла в начало раздела про город</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -817,7 +841,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>74,5 %</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -830,7 +858,11 @@
           <t>A = B</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>23 / 23</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -843,7 +875,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -856,7 +892,11 @@
           <t>position: sticky, top 90</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>sticky, top 90px</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -869,7 +909,11 @@
           <t>static, order 2, нет горизонтальной прокрутки</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>static, order 2, ширина документа 390</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -882,7 +926,11 @@
           <t>да</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>да: BlogPosting, Person, EducationalOrganization, FAQPage, BreadcrumbList</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -895,7 +943,11 @@
           <t>совпадение полное</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>6 вопросов и 6 ответов, совпадение полное</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -908,7 +960,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>0; ёлочек 12 пар</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -921,7 +977,11 @@
           <t>все верны</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>найдена и исправлена одна: «про стипендия CSC» → «про стипендию CSC»</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -934,7 +994,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>две исправлены: лежит → выложена, набегает → накапливается. Одна оставлена сознательно: «набегала сумма» внутри блока ИЗ ЛИЧНОГО ОПЫТА, там это живая речь</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -947,7 +1011,11 @@
           <t>есть, с запретом переноса</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>есть — унаследовано из статьи ДРУГ НА КИТАЙСКОМ, где было добавлено</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -960,7 +1028,11 @@
           <t>подбирается замером</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>525 px при содержимом до 503, запас 22</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -973,7 +1045,11 @@
           <t>0 на отдаче</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>найден и исправлен один, см. лист Картинки</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -986,7 +1062,11 @@
           <t>7 в исходнике / 5 в блоке, assets = 0</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>ждём ссылки от заказчика</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1898,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2027,13 +2107,34 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Дефекты рендеров</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr"/>
+          <t>ДЕФЕКТ 1. Обложка</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>под панелью поиска оставалось пустое поле почти в треть высоты</t>
+        </is>
+      </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>проставляется после просмотра</t>
+          <t>добавлен блок «Что находится по этому запросу» с двумя перечёркнутыми строками. Заодно усилилась метафора: вот что находится по запросу, а вот что нужно на самом деле</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Инфографика</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>дефектов не найдено</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>наложений, обрезанного текста и пустых полос нет, карточки одной высоты</t>
         </is>
       </c>
     </row>

--- a/content/tz-postuplenie-v-vuz-kitaya.xlsx
+++ b/content/tz-postuplenie-v-vuz-kitaya.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ПЛАН 40 000–45 000. ФАКТ 45 144 — на 144 знака выше границы, лимит 50 000 не нарушен. Лучшее попадание за четыре статьи</t>
+          <t>ПЛАН 40 000–45 000. ФАКТ 45 350 с адресами Tilda — на 350 знаков выше границы, лимит не нарушен, запас 4 650</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>45 144 — на 144 знака выше границы. Лучшее попадание за четыре статьи</t>
+          <t>45 350 с адресами Tilda — на 350 знаков выше границы. Лучшее попадание за четыре статьи</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>ждём ссылки от заказчика</t>
+          <t>7 / 5, assets = 0. ПОРЯДОК ПРОВЕРИТЬ НЕ УДАЛОСЬ: Tilda обрезала оба имени до одинакового postuplenie-v-vuz-ki.png, а прокси отдаёт 403 на оба адреса. Вшито по обычному порядку — первая обложка, вторая инфографика. ЭТО ПРЕДПОЛОЖЕНИЕ: заказчику надо посмотреть глазами</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com — подставляется после загрузки</t>
+          <t>https://static.tildacdn.com/tild3766-3836-4138-b438-353131663632/postuplenie-v-vuz-ki.png</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com</t>
+          <t>https://static.tildacdn.com/tild3766-3836-4138-b438-353131663632/postuplenie-v-vuz-ki.png</t>
         </is>
       </c>
     </row>
